--- a/手順.xlsx
+++ b/手順.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\woody\0woodyprojects\K2310\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C4B031F-B7CD-47B5-AA48-ACBD3CAE7FE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9929A672-41E9-42CE-93A9-D73677214343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="13546" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="49">
   <si>
     <t>frontend</t>
     <phoneticPr fontId="1"/>
@@ -183,6 +183,30 @@
   <si>
     <t>https://d188kdui0iet2x.cloudfront.net</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>8/20再デプロイ</t>
+    <rPh sb="4" eb="5">
+      <t>サイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>npm run build     # tsc で src/ → dist/ をビルド(新しいequipmentハンドラも含む)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>sam deploy         # samconfig.toml の設定を使って CloudFormation を更新</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>git add -A</t>
+  </si>
+  <si>
+    <t>git commit -m "..."</t>
+  </si>
+  <si>
+    <t>git push origin main</t>
   </si>
 </sst>
 </file>
@@ -222,12 +246,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -243,10 +279,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
@@ -528,7 +566,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="17.649999999999999"/>
   <cols>
     <col min="1" max="3" width="2.5625" customWidth="1"/>
@@ -594,19 +632,39 @@
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="2:2">
+    <row r="18" spans="1:4">
       <c r="B18" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="2:2">
+    <row r="19" spans="1:4">
       <c r="B19" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="2:2">
+    <row r="20" spans="1:4">
       <c r="B20" t="s">
         <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" s="3" customFormat="1">
+      <c r="A22" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="D24" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="D25" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="D26" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -617,7 +675,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74A57889-5990-46F5-8362-6AD0BD043A6E}">
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr defaultRowHeight="17.649999999999999"/>
   <cols>
     <col min="1" max="3" width="2.5625" customWidth="1"/>
@@ -717,7 +775,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="2:7">
+    <row r="17" spans="1:7">
       <c r="D17" t="s">
         <v>24</v>
       </c>
@@ -725,39 +783,61 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="2:7">
+    <row r="18" spans="1:7">
       <c r="C18" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="2:7">
+    <row r="21" spans="1:7">
       <c r="B21" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="2:7">
+    <row r="22" spans="1:7">
       <c r="B22" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="2:7">
+    <row r="24" spans="1:7">
       <c r="C24" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="25" spans="2:7">
+    <row r="25" spans="1:7">
       <c r="D25" s="2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="26" spans="2:7">
+    <row r="26" spans="1:7">
       <c r="C26" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="27" spans="2:7">
+    <row r="27" spans="1:7">
       <c r="D27" t="s">
         <v>40</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" s="3" customFormat="1">
+      <c r="A29" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="D30" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="B31" s="4"/>
+      <c r="D31" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="B32" s="4"/>
+      <c r="D32" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/手順.xlsx
+++ b/手順.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\woody\0woodyprojects\K2310\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9929A672-41E9-42CE-93A9-D73677214343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{064A0134-39F1-4B5C-9AD9-98754903119B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="13546" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="13546" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="frontend" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="50">
   <si>
     <t>frontend</t>
     <phoneticPr fontId="1"/>
@@ -201,19 +201,31 @@
   </si>
   <si>
     <t>git add -A</t>
-  </si>
-  <si>
-    <t>git commit -m "..."</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>git commit -m "備品タブ完成"</t>
+    <rPh sb="15" eb="17">
+      <t>ビヒン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>カンセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>git push origin main</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VITE_API_URL は既に CloudFormation 経由で Amplify に自動設定されているので、変更不要です。main ブランチに push すれば EnableAutoBuild: true により Amplify が自動でビルド・デプロイします。</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -243,6 +255,13 @@
       <color theme="10"/>
       <name val="Yu Gothic"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -279,12 +298,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
@@ -566,7 +586,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="17.649999999999999"/>
   <cols>
     <col min="1" max="3" width="2.5625" customWidth="1"/>
@@ -653,17 +673,25 @@
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="D24" t="s">
+      <c r="B24" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="B25" s="4"/>
+      <c r="D25" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
-      <c r="D25" t="s">
+    <row r="26" spans="1:4">
+      <c r="B26" s="4"/>
+      <c r="D26" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
-      <c r="D26" t="s">
+    <row r="27" spans="1:4">
+      <c r="B27" s="4"/>
+      <c r="D27" t="s">
         <v>48</v>
       </c>
     </row>

--- a/手順.xlsx
+++ b/手順.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\woody\0woodyprojects\K2310\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{064A0134-39F1-4B5C-9AD9-98754903119B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF96D946-A6B1-4BD2-99D9-373B314D6C53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="13546" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="13546" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="frontend" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="52">
   <si>
     <t>frontend</t>
     <phoneticPr fontId="1"/>
@@ -189,14 +189,6 @@
     <rPh sb="4" eb="5">
       <t>サイ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>npm run build     # tsc で src/ → dist/ をビルド(新しいequipmentハンドラも含む)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>sam deploy         # samconfig.toml の設定を使って CloudFormation を更新</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -219,6 +211,22 @@
   </si>
   <si>
     <t>VITE_API_URL は既に CloudFormation 経由で Amplify に自動設定されているので、変更不要です。main ブランチに push すれば EnableAutoBuild: true により Amplify が自動でビルド・デプロイします。</t>
+  </si>
+  <si>
+    <t># tsc で src/ → dist/ をビルド(新しいequipmentハンドラも含む)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>npm run build</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t># samconfig.toml の設定を使って CloudFormation を更新</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>sam deploy</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -674,25 +682,25 @@
     </row>
     <row r="24" spans="1:4">
       <c r="B24" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="B25" s="4"/>
       <c r="D25" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="B26" s="4"/>
       <c r="D26" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="B27" s="4"/>
       <c r="D27" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -859,13 +867,19 @@
     <row r="31" spans="1:7">
       <c r="B31" s="4"/>
       <c r="D31" t="s">
-        <v>44</v>
+        <v>49</v>
+      </c>
+      <c r="F31" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="B32" s="4"/>
       <c r="D32" t="s">
-        <v>45</v>
+        <v>51</v>
+      </c>
+      <c r="F32" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/手順.xlsx
+++ b/手順.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\woody\0woodyprojects\K2310\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF96D946-A6B1-4BD2-99D9-373B314D6C53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C1E8135-3C6A-4F4A-ADED-53DFCCA35998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="13546" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="51">
   <si>
     <t>frontend</t>
     <phoneticPr fontId="1"/>
@@ -42,9 +42,6 @@
     <t># 1. TypeScript をビルド（dist/ に出力）</t>
   </si>
   <si>
-    <t>npm run build</t>
-  </si>
-  <si>
     <t># 2. 初回のみ: ガイド付きデプロイ設定（samconfig.toml が生成される）</t>
   </si>
   <si>
@@ -52,9 +49,6 @@
   </si>
   <si>
     <t># 3. 2回目以降</t>
-  </si>
-  <si>
-    <t>sam deploy</t>
   </si>
   <si>
     <t>Stack Name</t>
@@ -226,6 +220,10 @@
   </si>
   <si>
     <t>sam deploy</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(aws login)</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -607,100 +605,100 @@
     </row>
     <row r="2" spans="1:2">
       <c r="B2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="B5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="B6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="B7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="B8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="B9" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="B11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="B12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="B13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="B15" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="B16" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="B18" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="B19" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="B20" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:4" s="3" customFormat="1">
       <c r="A22" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="B24" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="B25" s="4"/>
       <c r="D25" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="B26" s="4"/>
       <c r="D26" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="B27" s="4"/>
       <c r="D27" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -727,136 +725,142 @@
         <v>2</v>
       </c>
     </row>
+    <row r="3" spans="1:7">
+      <c r="B3" t="s">
+        <v>50</v>
+      </c>
+    </row>
     <row r="4" spans="1:7">
       <c r="B4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:7">
+      <c r="A5" s="4"/>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="B7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="B8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="D9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="D10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="D11" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="D12" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="D13" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="D14" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="D15" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="D16" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="D17" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="C18" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="B21" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="B22" t="s">
-        <v>8</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="C24" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="D25" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="C26" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="D27" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:7" s="3" customFormat="1">
       <c r="A29" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -867,19 +871,19 @@
     <row r="31" spans="1:7">
       <c r="B31" s="4"/>
       <c r="D31" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F31" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="B32" s="4"/>
       <c r="D32" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F32" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
